--- a/KYC_review.xlsx
+++ b/KYC_review.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm:ss"/>
+  </numFmts>
   <fonts count="4">
     <font>
       <name val="Arial"/>
@@ -66,7 +69,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -77,6 +80,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -269,8 +273,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="20" customWidth="1" style="2" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1" ht="12.8" customHeight="1" s="2">
       <c r="A1" s="3" t="inlineStr">
@@ -313,3706 +320,4011 @@
           <t>Reason</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Entered Queue</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="12.8" customHeight="1" s="2">
-      <c r="A2" t="n">
+      <c r="A2" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Eve Baker</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Eve Baker</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>637</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>[Travel Ban]</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Inconsistent information from sanctions lists</t>
         </is>
       </c>
+      <c r="I2" s="4" t="n">
+        <v>46267.17873842592</v>
+      </c>
     </row>
     <row r="3" ht="12.8" customHeight="1" s="2">
-      <c r="A3" t="n">
+      <c r="A3" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Yvonne Roberts</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Y. Roberts</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="n">
         <v>662</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Name read from id doesn’t exactly match customer name</t>
         </is>
       </c>
+      <c r="I3" s="4" t="n">
+        <v>46267.4411574074</v>
+      </c>
     </row>
     <row r="4" ht="12.8" customHeight="1" s="2">
-      <c r="A4" t="n">
+      <c r="A4" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>David Thomas</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>David Thomas</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Missing credit score</t>
         </is>
       </c>
+      <c r="I4" s="4" t="n">
+        <v>46267.07104166667</v>
+      </c>
     </row>
     <row r="5" ht="12.8" customHeight="1" s="2">
-      <c r="A5" t="n">
+      <c r="A5" s="3" t="n">
         <v>62</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Ulrich Hall</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Ulrich Hall</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="3" t="n">
         <v>687</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>[Asset Freeze]</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Inconsistent information from sanctions lists</t>
         </is>
       </c>
+      <c r="I5" s="4" t="n">
+        <v>46266.68251157407</v>
+      </c>
     </row>
     <row r="6" ht="12.8" customHeight="1" s="2">
-      <c r="A6" t="n">
+      <c r="A6" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Karen Parker</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Karen Parkes</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="3" t="n">
         <v>711</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Name read from id doesn’t exactly match customer name</t>
         </is>
       </c>
+      <c r="I6" s="4" t="n">
+        <v>46267.59675925926</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Felix Hall</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Felix Hall</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Missing credit score</t>
         </is>
       </c>
+      <c r="I7" s="4" t="n">
+        <v>46267.56011574074</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Julia Roberts</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Julia Roberts</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="3" t="n">
         <v>621</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>[Travel Ban]</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>Inconsistent information from sanctions lists</t>
         </is>
       </c>
+      <c r="I8" s="4" t="n">
+        <v>46266.85704861111</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="3" t="n">
         <v>143</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Isabel Roberts</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Roberts Isabel</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>769</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>Name read from id doesn’t exactly match customer name</t>
         </is>
       </c>
+      <c r="I9" s="4" t="n">
+        <v>46267.52721064815</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="3" t="n">
         <v>162</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Xavier Thomas</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Xavier Thomas</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>Missing credit score</t>
         </is>
       </c>
+      <c r="I10" s="4" t="n">
+        <v>46267.11524305555</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="3" t="n">
         <v>164</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Georgia Hughes</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Georgia Hughes</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="3" t="n">
         <v>596</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>[Asset Freeze]</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>Inconsistent information from sanctions lists</t>
         </is>
       </c>
+      <c r="I11" s="4" t="n">
+        <v>46266.7858912037</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="3" t="n">
         <v>179</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Julia Harris</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Harris Julia</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="3" t="n">
         <v>631</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>Name read from id doesn’t exactly match customer name</t>
         </is>
       </c>
+      <c r="I12" s="4" t="n">
+        <v>46267.58201388889</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="3" t="n">
         <v>190</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Maria Brown</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Maria Brown</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>Missing credit score</t>
         </is>
       </c>
+      <c r="I13" s="4" t="n">
+        <v>46266.90020833333</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="3" t="n">
         <v>192</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Yvonne Baker</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Yvonne Baker</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="3" t="n">
         <v>789</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>[Arms Embargo]</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>Inconsistent information from sanctions lists</t>
         </is>
       </c>
+      <c r="I14" s="4" t="n">
+        <v>46267.34430555555</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" s="3" t="n">
         <v>199</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Alice Martin</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>A. Martin</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="3" t="n">
         <v>608</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>Name read from id doesn’t exactly match customer name</t>
         </is>
       </c>
+      <c r="I15" s="4" t="n">
+        <v>46267.613125</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" s="3" t="n">
         <v>207</v>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Victor Taylor</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Victor Taylor</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>Missing credit score</t>
         </is>
       </c>
+      <c r="I16" s="4" t="n">
+        <v>46267.53961805555</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="3" t="n">
         <v>210</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Benjamin Davies</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Benjamin Davies</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="3" t="n">
         <v>782</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>[Asset Freeze]</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>Inconsistent information from sanctions lists</t>
         </is>
       </c>
+      <c r="I17" s="4" t="n">
+        <v>46267.01215277778</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18" s="3" t="n">
         <v>229</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Quentin Edwards</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Quentiny Edwards</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="3" t="n">
         <v>641</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>Name read from id doesn’t exactly match customer name</t>
         </is>
       </c>
+      <c r="I18" s="4" t="n">
+        <v>46267.035625</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
+      <c r="A19" s="3" t="n">
         <v>256</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Tina Moore</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Tina Moore</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>Missing credit score</t>
         </is>
       </c>
+      <c r="I19" s="4" t="n">
+        <v>46267.56402777778</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
+      <c r="A20" s="3" t="n">
         <v>286</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Maria Evans</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Maria Evans</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="3" t="n">
         <v>628</v>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>[Arms Embargo]</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>Inconsistent information from sanctions lists</t>
         </is>
       </c>
+      <c r="I20" s="4" t="n">
+        <v>46267.30490740741</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
+      <c r="A21" s="3" t="n">
         <v>319</v>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Isabel Hill</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>I. Hill</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="3" t="n">
         <v>550</v>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>Name read from id doesn’t exactly match customer name</t>
         </is>
       </c>
+      <c r="I21" s="4" t="n">
+        <v>46267.53239583333</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
+      <c r="A22" s="3" t="n">
         <v>327</v>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Felix Smith</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Felix Smith</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>Missing credit score</t>
         </is>
       </c>
+      <c r="I22" s="4" t="n">
+        <v>46266.83405092593</v>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
+      <c r="A23" s="3" t="n">
         <v>334</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Xavier Parker</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Xavier Parker</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="3" t="n">
         <v>707</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>[Travel Ban]</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>Inconsistent information from sanctions lists</t>
         </is>
       </c>
+      <c r="I23" s="4" t="n">
+        <v>46267.02599537037</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
+      <c r="A24" s="3" t="n">
         <v>394</v>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Karen Brown</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>Brown Karen</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="3" t="n">
         <v>593</v>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>Name read from id doesn’t exactly match customer name</t>
         </is>
       </c>
+      <c r="I24" s="4" t="n">
+        <v>46267.58033564815</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
+      <c r="A25" s="3" t="n">
         <v>408</v>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Eve Hill</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Eve Hill</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>Missing credit score</t>
         </is>
       </c>
+      <c r="I25" s="4" t="n">
+        <v>46266.8121875</v>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
+      <c r="A26" s="3" t="n">
         <v>430</v>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Ivan Martin</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Ivan Martin</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="3" t="n">
         <v>793</v>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>[Travel Ban]</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>Inconsistent information from sanctions lists</t>
         </is>
       </c>
+      <c r="I26" s="4" t="n">
+        <v>46267.48219907407</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
+      <c r="A27" s="3" t="n">
         <v>441</v>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Maria Wood</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>Maria Woos</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="3" t="n">
         <v>658</v>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>Name read from id doesn’t exactly match customer name</t>
         </is>
       </c>
+      <c r="I27" s="4" t="n">
+        <v>46267.3313425926</v>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
+      <c r="A28" s="3" t="n">
         <v>448</v>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Tina Hall</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>Tina Hall</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>Missing credit score</t>
         </is>
       </c>
+      <c r="I28" s="4" t="n">
+        <v>46266.71332175926</v>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
+      <c r="A29" s="3" t="n">
         <v>452</v>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Chloe Parker</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>Chloe Parker</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="3" t="n">
         <v>814</v>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>[PEP]</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>Inconsistent information from sanctions lists</t>
         </is>
       </c>
+      <c r="I29" s="4" t="n">
+        <v>46266.7181712963</v>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
+      <c r="A30" s="3" t="n">
         <v>458</v>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Oscar Brown</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>Oscary Brown</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="3" t="n">
         <v>723</v>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>Name read from id doesn’t exactly match customer name</t>
         </is>
       </c>
+      <c r="I30" s="4" t="n">
+        <v>46266.7855787037</v>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
+      <c r="A31" s="3" t="n">
         <v>467</v>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Liam Lewis</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>Liam Lewis</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>Missing credit score</t>
         </is>
       </c>
+      <c r="I31" s="4" t="n">
+        <v>46267.57615740741</v>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
+      <c r="A32" s="3" t="n">
         <v>477</v>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Liam Thomas</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>Liam Thomas</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="3" t="n">
         <v>553</v>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>[Asset Freeze]</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>Inconsistent information from sanctions lists</t>
         </is>
       </c>
+      <c r="I32" s="4" t="n">
+        <v>46266.79451388889</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
+      <c r="A33" s="3" t="n">
         <v>502</v>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>David Thomas</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>Davidy Thomas</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="3" t="n">
         <v>584</v>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>Name read from id doesn’t exactly match customer name</t>
         </is>
       </c>
+      <c r="I33" s="4" t="n">
+        <v>46266.78171296296</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
+      <c r="A34" s="3" t="n">
         <v>542</v>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Victor Brown</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>Victor Brown</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>Missing credit score</t>
         </is>
       </c>
+      <c r="I34" s="4" t="n">
+        <v>46267.06822916667</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
+      <c r="A35" s="3" t="n">
         <v>547</v>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>Paula Roberts</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>Paula Roberts</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="3" t="n">
         <v>798</v>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>[Travel Ban]</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>Inconsistent information from sanctions lists</t>
         </is>
       </c>
+      <c r="I35" s="4" t="n">
+        <v>46267.59478009259</v>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
+      <c r="A36" s="3" t="n">
         <v>564</v>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Karen King</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>Karen Kins</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="3" t="n">
         <v>792</v>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t>Name read from id doesn’t exactly match customer name</t>
         </is>
       </c>
+      <c r="I36" s="4" t="n">
+        <v>46267.33461805555</v>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
+      <c r="A37" s="3" t="n">
         <v>570</v>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>Elena Ward</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>Elena Ward</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>Missing credit score</t>
         </is>
       </c>
+      <c r="I37" s="4" t="n">
+        <v>46267.59934027777</v>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
+      <c r="A38" s="3" t="n">
         <v>593</v>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>Michael Taylor</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>Michael Taylor</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="3" t="n">
         <v>599</v>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>[PEP]</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t>Inconsistent information from sanctions lists</t>
         </is>
       </c>
+      <c r="I38" s="4" t="n">
+        <v>46266.82552083334</v>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
+      <c r="A39" s="3" t="n">
         <v>601</v>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>Amelia Clarke</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>Ameliay Clarke</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="3" t="n">
         <v>577</v>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t>Name read from id doesn’t exactly match customer name</t>
         </is>
       </c>
+      <c r="I39" s="4" t="n">
+        <v>46267.46797453704</v>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
+      <c r="A40" s="3" t="n">
         <v>690</v>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>David Hall</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>David Hall</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <t>Missing credit score</t>
         </is>
       </c>
+      <c r="I40" s="4" t="n">
+        <v>46267.23065972222</v>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
+      <c r="A41" s="3" t="n">
         <v>697</v>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>Grace Thomas</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>Grace Thomas</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="3" t="n">
         <v>648</v>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>[Travel Ban]</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
         <is>
           <t>Inconsistent information from sanctions lists</t>
         </is>
       </c>
+      <c r="I41" s="4" t="n">
+        <v>46267.0341550926</v>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
+      <c r="A42" s="3" t="n">
         <v>705</v>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>Ivan Wood</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>I. Wood</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="3" t="n">
         <v>643</v>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t>Name read from id doesn’t exactly match customer name</t>
         </is>
       </c>
+      <c r="I42" s="4" t="n">
+        <v>46267.45116898148</v>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
+      <c r="A43" s="3" t="n">
         <v>728</v>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>Daniel Thomas</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>Daniel Thomas</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
         <is>
           <t>Missing credit score</t>
         </is>
       </c>
+      <c r="I43" s="4" t="n">
+        <v>46266.84976851852</v>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
+      <c r="A44" s="3" t="n">
         <v>736</v>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>Chloe Ward</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>Chloe Ward</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
         <is>
           <t>[Asset Freeze]</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
         <is>
           <t>Inconsistent information from sanctions lists</t>
         </is>
       </c>
+      <c r="I44" s="4" t="n">
+        <v>46267.49130787037</v>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
+      <c r="A45" s="3" t="n">
         <v>741</v>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>Isabel Moore</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>Isabely Moore</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="3" t="n">
         <v>557</v>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
         <is>
           <t>Name read from id doesn’t exactly match customer name</t>
         </is>
       </c>
+      <c r="I45" s="4" t="n">
+        <v>46266.80391203704</v>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="n">
+      <c r="A46" s="3" t="n">
         <v>748</v>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>Paula Davies</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>Paula Davies</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
         <is>
           <t>Missing credit score</t>
         </is>
       </c>
+      <c r="I46" s="4" t="n">
+        <v>46267.20202546296</v>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
+      <c r="A47" s="3" t="n">
         <v>759</v>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>Felix Hughes</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>Felix Hughes</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="3" t="n">
         <v>659</v>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>[PEP]</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
         <is>
           <t>Inconsistent information from sanctions lists</t>
         </is>
       </c>
+      <c r="I47" s="4" t="n">
+        <v>46266.82006944445</v>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
+      <c r="A48" s="3" t="n">
         <v>776</v>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>Kevin Hall</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>Hall Kevin</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="3" t="n">
         <v>551</v>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
         <is>
           <t>Name read from id doesn’t exactly match customer name</t>
         </is>
       </c>
+      <c r="I48" s="4" t="n">
+        <v>46267.39583333334</v>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
+      <c r="A49" s="3" t="n">
         <v>779</v>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>Quentin Cook</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>Quentin Cook</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
         <is>
           <t>Missing credit score</t>
         </is>
       </c>
+      <c r="I49" s="4" t="n">
+        <v>46267.51366898148</v>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" t="n">
+      <c r="A50" s="3" t="n">
         <v>860</v>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>Samuel Wood</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>Samuel Wood</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="3" t="n">
         <v>799</v>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="3" t="inlineStr">
         <is>
           <t>[Travel Ban]</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
         <is>
           <t>Inconsistent information from sanctions lists</t>
         </is>
       </c>
+      <c r="I50" s="4" t="n">
+        <v>46266.78769675926</v>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
+      <c r="A51" s="3" t="n">
         <v>865</v>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>Nina Johnson</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>N. Johnson</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="3" t="n">
         <v>581</v>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
         <is>
           <t>Name read from id doesn’t exactly match customer name</t>
         </is>
       </c>
+      <c r="I51" s="4" t="n">
+        <v>46266.80347222222</v>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" t="n">
+      <c r="A52" s="3" t="n">
         <v>866</v>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>David Johnson</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>David Johnson</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
         <is>
           <t>Missing credit score</t>
         </is>
       </c>
+      <c r="I52" s="4" t="n">
+        <v>46266.70075231481</v>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" t="n">
+      <c r="A53" s="3" t="n">
         <v>920</v>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>Georgia Cook</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>Georgia Cook</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="3" t="n">
         <v>630</v>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>[Asset Freeze]</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
         <is>
           <t>Inconsistent information from sanctions lists</t>
         </is>
       </c>
+      <c r="I53" s="4" t="n">
+        <v>46267.385</v>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" t="n">
+      <c r="A54" s="3" t="n">
         <v>929</v>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>Frank Clark</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>Franky Clark</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="3" t="n">
         <v>645</v>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
         <is>
           <t>Name read from id doesn’t exactly match customer name</t>
         </is>
       </c>
+      <c r="I54" s="4" t="n">
+        <v>46267.10506944444</v>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" t="n">
+      <c r="A55" s="3" t="n">
         <v>941</v>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>Maria Brown</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>Maria Brown</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
         <is>
           <t>Missing credit score</t>
         </is>
       </c>
+      <c r="I55" s="4" t="n">
+        <v>46267.52219907408</v>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" t="n">
+      <c r="A56" s="3" t="n">
         <v>1035</v>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>Zach Taylor</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>Zach Taylor</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="3" t="n">
         <v>676</v>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
         <is>
           <t>[Asset Freeze]</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
         <is>
           <t>Inconsistent information from sanctions lists</t>
         </is>
       </c>
+      <c r="I56" s="4" t="n">
+        <v>46266.8390625</v>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" t="n">
+      <c r="A57" s="3" t="n">
         <v>1099</v>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>Amelia Martin</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>A. Martin</t>
         </is>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="3" t="n">
         <v>817</v>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
         <is>
           <t>Name read from id doesn’t exactly match customer name</t>
         </is>
       </c>
+      <c r="I57" s="4" t="n">
+        <v>46267.57475694444</v>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" t="n">
+      <c r="A58" s="3" t="n">
         <v>1117</v>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>Quentin Evans</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>Quentin Evans</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
         <is>
           <t>Missing credit score</t>
         </is>
       </c>
+      <c r="I58" s="4" t="n">
+        <v>46266.81384259259</v>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" t="n">
+      <c r="A59" s="3" t="n">
         <v>1131</v>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>Paula Roberts</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>Paula Roberts</t>
         </is>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="3" t="n">
         <v>752</v>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t>[Travel Ban]</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
         <is>
           <t>Inconsistent information from sanctions lists</t>
         </is>
       </c>
+      <c r="I59" s="4" t="n">
+        <v>46267.57958333333</v>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" t="n">
+      <c r="A60" s="3" t="n">
         <v>1150</v>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>Tina Clarke</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>Tinay Clarke</t>
         </is>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="3" t="n">
         <v>711</v>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
         <is>
           <t>Name read from id doesn’t exactly match customer name</t>
         </is>
       </c>
+      <c r="I60" s="4" t="n">
+        <v>46266.73094907407</v>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" t="n">
+      <c r="A61" s="3" t="n">
         <v>1183</v>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>Alice Clarke</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>Alice Clarke</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
         <is>
           <t>Missing credit score</t>
         </is>
       </c>
+      <c r="I61" s="4" t="n">
+        <v>46267.35755787037</v>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" t="n">
+      <c r="A62" s="3" t="n">
         <v>1207</v>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>Eve Lewis</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>Eve Lewis</t>
         </is>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="3" t="n">
         <v>659</v>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E62" s="3" t="inlineStr">
         <is>
           <t>[Arms Embargo]</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
         <is>
           <t>Inconsistent information from sanctions lists</t>
         </is>
       </c>
+      <c r="I62" s="4" t="n">
+        <v>46266.9169212963</v>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" t="n">
+      <c r="A63" s="3" t="n">
         <v>1210</v>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>Wendy Parker</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>Wendy Parkes</t>
         </is>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" s="3" t="n">
         <v>585</v>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
         <is>
           <t>Name read from id doesn’t exactly match customer name</t>
         </is>
       </c>
+      <c r="I63" s="4" t="n">
+        <v>46266.86336805556</v>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" t="n">
+      <c r="A64" s="3" t="n">
         <v>1233</v>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>Xavier Walker</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>Xavier Walker</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
         <is>
           <t>Missing credit score</t>
         </is>
       </c>
+      <c r="I64" s="4" t="n">
+        <v>46267.02133101852</v>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" t="n">
+      <c r="A65" s="3" t="n">
         <v>1237</v>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>Chloe Moore</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>Chloe Moore</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="3" t="n">
         <v>704</v>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
         <is>
           <t>[Asset Freeze]</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
         <is>
           <t>Inconsistent information from sanctions lists</t>
         </is>
       </c>
+      <c r="I65" s="4" t="n">
+        <v>46267.1934375</v>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" t="n">
+      <c r="A66" s="3" t="n">
         <v>1267</v>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>Jack Walker</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>Jack Walkes</t>
         </is>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" s="3" t="n">
         <v>603</v>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
         <is>
           <t>Name read from id doesn’t exactly match customer name</t>
         </is>
       </c>
+      <c r="I66" s="4" t="n">
+        <v>46266.96366898148</v>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" t="n">
+      <c r="A67" s="3" t="n">
         <v>1288</v>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>Quentin Taylor</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>Quentin Taylor</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
         <is>
           <t>Missing credit score</t>
         </is>
       </c>
+      <c r="I67" s="4" t="n">
+        <v>46266.78168981482</v>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" t="n">
+      <c r="A68" s="3" t="n">
         <v>1302</v>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>Jack Wilson</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>Jack Wilson</t>
         </is>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="3" t="n">
         <v>689</v>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
         <is>
           <t>[Arms Embargo]</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
         <is>
           <t>Inconsistent information from sanctions lists</t>
         </is>
       </c>
+      <c r="I68" s="4" t="n">
+        <v>46266.98251157408</v>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
+      <c r="A69" s="3" t="n">
         <v>1310</v>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>Victor Evans</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>Evans Victor</t>
         </is>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="3" t="n">
         <v>685</v>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
         <is>
           <t>Name read from id doesn’t exactly match customer name</t>
         </is>
       </c>
+      <c r="I69" s="4" t="n">
+        <v>46267.1214699074</v>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" t="n">
+      <c r="A70" s="3" t="n">
         <v>1331</v>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>Quentin Parker</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>Quentin Parker</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
         <is>
           <t>Missing credit score</t>
         </is>
       </c>
+      <c r="I70" s="4" t="n">
+        <v>46267.21524305556</v>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" t="n">
+      <c r="A71" s="3" t="n">
         <v>1355</v>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>Frank Harris</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>Frank Harris</t>
         </is>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="3" t="n">
         <v>766</v>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E71" s="3" t="inlineStr">
         <is>
           <t>[Arms Embargo]</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
         <is>
           <t>Inconsistent information from sanctions lists</t>
         </is>
       </c>
+      <c r="I71" s="4" t="n">
+        <v>46267.29313657407</v>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" t="n">
+      <c r="A72" s="3" t="n">
         <v>1373</v>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>Victor Hill</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>V. Hill</t>
         </is>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" s="3" t="n">
         <v>616</v>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
         <is>
           <t>Name read from id doesn’t exactly match customer name</t>
         </is>
       </c>
+      <c r="I72" s="4" t="n">
+        <v>46267.39729166667</v>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" t="n">
+      <c r="A73" s="3" t="n">
         <v>1386</v>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>Kevin Turner</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>Kevin Turner</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
         <is>
           <t>Missing credit score</t>
         </is>
       </c>
+      <c r="I73" s="4" t="n">
+        <v>46267.29969907407</v>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" t="n">
+      <c r="A74" s="3" t="n">
         <v>1430</v>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>Jack Cooper</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>Jack Cooper</t>
         </is>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" s="3" t="n">
         <v>768</v>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E74" s="3" t="inlineStr">
         <is>
           <t>[Asset Freeze]</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
         <is>
           <t>Inconsistent information from sanctions lists</t>
         </is>
       </c>
+      <c r="I74" s="4" t="n">
+        <v>46267.54583333333</v>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" t="n">
+      <c r="A75" s="3" t="n">
         <v>1437</v>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>Julia Lewis</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>J. Lewis</t>
         </is>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="3" t="n">
         <v>568</v>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
         <is>
           <t>Name read from id doesn’t exactly match customer name</t>
         </is>
       </c>
+      <c r="I75" s="4" t="n">
+        <v>46266.79858796296</v>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" t="n">
+      <c r="A76" s="3" t="n">
         <v>1438</v>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>Liam Lewis</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>Liam Lewis</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
         <is>
           <t>Missing credit score</t>
         </is>
       </c>
+      <c r="I76" s="4" t="n">
+        <v>46267.21451388889</v>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" t="n">
+      <c r="A77" s="3" t="n">
         <v>1443</v>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>Benjamin Wilson</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>Benjamin Wilson</t>
         </is>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="3" t="n">
         <v>571</v>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E77" s="3" t="inlineStr">
         <is>
           <t>[Arms Embargo]</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
         <is>
           <t>Inconsistent information from sanctions lists</t>
         </is>
       </c>
+      <c r="I77" s="4" t="n">
+        <v>46266.87326388889</v>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" t="n">
+      <c r="A78" s="3" t="n">
         <v>1467</v>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>Charlie Parker</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>Charlie Parkes</t>
         </is>
       </c>
-      <c r="D78" t="n">
+      <c r="D78" s="3" t="n">
         <v>733</v>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
         <is>
           <t>Name read from id doesn’t exactly match customer name</t>
         </is>
       </c>
+      <c r="I78" s="4" t="n">
+        <v>46266.91890046297</v>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" t="n">
+      <c r="A79" s="3" t="n">
         <v>1495</v>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>Paula Martin</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t>Paula Martin</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
         <is>
           <t>Missing credit score</t>
         </is>
       </c>
+      <c r="I79" s="4" t="n">
+        <v>46267.14893518519</v>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" t="n">
+      <c r="A80" s="3" t="n">
         <v>1509</v>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>Wendy Hill</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t>Wendy Hill</t>
         </is>
       </c>
-      <c r="D80" t="n">
+      <c r="D80" s="3" t="n">
         <v>758</v>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
         <is>
           <t>[Travel Ban]</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
         <is>
           <t>Inconsistent information from sanctions lists</t>
         </is>
       </c>
+      <c r="I80" s="4" t="n">
+        <v>46266.9891087963</v>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" t="n">
+      <c r="A81" s="3" t="n">
         <v>1517</v>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>Paula Clark</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>Paula Clars</t>
         </is>
       </c>
-      <c r="D81" t="n">
+      <c r="D81" s="3" t="n">
         <v>633</v>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
         <is>
           <t>Name read from id doesn’t exactly match customer name</t>
         </is>
       </c>
+      <c r="I81" s="4" t="n">
+        <v>46267.23319444444</v>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" t="n">
+      <c r="A82" s="3" t="n">
         <v>1519</v>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="3" t="inlineStr">
         <is>
           <t>Amelia Smith</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="3" t="inlineStr">
         <is>
           <t>Amelia Smith</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
         <is>
           <t>Missing credit score</t>
         </is>
       </c>
+      <c r="I82" s="4" t="n">
+        <v>46266.74619212963</v>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" t="n">
+      <c r="A83" s="3" t="n">
         <v>1555</v>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t>Victor Ward</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C83" s="3" t="inlineStr">
         <is>
           <t>Victor Ward</t>
         </is>
       </c>
-      <c r="D83" t="n">
+      <c r="D83" s="3" t="n">
         <v>760</v>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="E83" s="3" t="inlineStr">
         <is>
           <t>[Travel Ban]</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
         <is>
           <t>Inconsistent information from sanctions lists</t>
         </is>
       </c>
+      <c r="I83" s="4" t="n">
+        <v>46267.55895833333</v>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" t="n">
+      <c r="A84" s="3" t="n">
         <v>1564</v>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
         <is>
           <t>Grace Hall</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t>Hall Grace</t>
         </is>
       </c>
-      <c r="D84" t="n">
+      <c r="D84" s="3" t="n">
         <v>569</v>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
         <is>
           <t>Name read from id doesn’t exactly match customer name</t>
         </is>
       </c>
+      <c r="I84" s="4" t="n">
+        <v>46267.49089120371</v>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" t="n">
+      <c r="A85" s="3" t="n">
         <v>1584</v>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="3" t="inlineStr">
         <is>
           <t>Oscar Evans</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="3" t="inlineStr">
         <is>
           <t>Oscar Evans</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
         <is>
           <t>Missing credit score</t>
         </is>
       </c>
+      <c r="I85" s="4" t="n">
+        <v>46266.89337962963</v>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" t="n">
+      <c r="A86" s="3" t="n">
         <v>1651</v>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t>Wendy Walker</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="3" t="inlineStr">
         <is>
           <t>Wendy Walker</t>
         </is>
       </c>
-      <c r="D86" t="n">
+      <c r="D86" s="3" t="n">
         <v>666</v>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E86" s="3" t="inlineStr">
         <is>
           <t>[Travel Ban]</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
         <is>
           <t>Inconsistent information from sanctions lists</t>
         </is>
       </c>
+      <c r="I86" s="4" t="n">
+        <v>46267.03569444444</v>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" t="n">
+      <c r="A87" s="3" t="n">
         <v>1653</v>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="3" t="inlineStr">
         <is>
           <t>Michael Hall</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="3" t="inlineStr">
         <is>
           <t>M. Hall</t>
         </is>
       </c>
-      <c r="D87" t="n">
+      <c r="D87" s="3" t="n">
         <v>718</v>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
         <is>
           <t>Name read from id doesn’t exactly match customer name</t>
         </is>
       </c>
+      <c r="I87" s="4" t="n">
+        <v>46267.41975694444</v>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" t="n">
+      <c r="A88" s="3" t="n">
         <v>1658</v>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="3" t="inlineStr">
         <is>
           <t>Eve Hill</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C88" s="3" t="inlineStr">
         <is>
           <t>Eve Hill</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
         <is>
           <t>Missing credit score</t>
         </is>
       </c>
+      <c r="I88" s="4" t="n">
+        <v>46267.15109953703</v>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" t="n">
+      <c r="A89" s="3" t="n">
         <v>1699</v>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t>Wendy Harris</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="3" t="inlineStr">
         <is>
           <t>Wendy Harris</t>
         </is>
       </c>
-      <c r="D89" t="n">
+      <c r="D89" s="3" t="n">
         <v>810</v>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
         <is>
           <t>[PEP]</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
         <is>
           <t>Inconsistent information from sanctions lists</t>
         </is>
       </c>
+      <c r="I89" s="4" t="n">
+        <v>46267.43944444445</v>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" t="n">
+      <c r="A90" s="3" t="n">
         <v>1709</v>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t>Isabel Wright</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>Isabely Wright</t>
         </is>
       </c>
-      <c r="D90" t="n">
+      <c r="D90" s="3" t="n">
         <v>564</v>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
         <is>
           <t>Name read from id doesn’t exactly match customer name</t>
         </is>
       </c>
+      <c r="I90" s="4" t="n">
+        <v>46266.92822916667</v>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" t="n">
+      <c r="A91" s="3" t="n">
         <v>1736</v>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>Quentin Davies</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>Quentin Davies</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
         <is>
           <t>Missing credit score</t>
         </is>
       </c>
+      <c r="I91" s="4" t="n">
+        <v>46267.03027777778</v>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" t="n">
+      <c r="A92" s="3" t="n">
         <v>1752</v>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="3" t="inlineStr">
         <is>
           <t>Charlie Taylor</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C92" s="3" t="inlineStr">
         <is>
           <t>Charlie Taylor</t>
         </is>
       </c>
-      <c r="D92" t="n">
+      <c r="D92" s="3" t="n">
         <v>772</v>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
         <is>
           <t>[Arms Embargo]</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
         <is>
           <t>Inconsistent information from sanctions lists</t>
         </is>
       </c>
+      <c r="I92" s="4" t="n">
+        <v>46267.61053240741</v>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" t="n">
+      <c r="A93" s="3" t="n">
         <v>1765</v>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B93" s="3" t="inlineStr">
         <is>
           <t>Ulrich Wood</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C93" s="3" t="inlineStr">
         <is>
           <t>Ulrichy Wood</t>
         </is>
       </c>
-      <c r="D93" t="n">
+      <c r="D93" s="3" t="n">
         <v>811</v>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
         <is>
           <t>Name read from id doesn’t exactly match customer name</t>
         </is>
       </c>
+      <c r="I93" s="4" t="n">
+        <v>46267.55225694444</v>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" t="n">
+      <c r="A94" s="3" t="n">
         <v>1775</v>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B94" s="3" t="inlineStr">
         <is>
           <t>Yvonne Parker</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" s="3" t="inlineStr">
         <is>
           <t>Yvonne Parker</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
         <is>
           <t>Missing credit score</t>
         </is>
       </c>
+      <c r="I94" s="4" t="n">
+        <v>46266.82337962963</v>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" t="n">
+      <c r="A95" s="3" t="n">
         <v>1781</v>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="3" t="inlineStr">
         <is>
           <t>Quentin Johnson</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C95" s="3" t="inlineStr">
         <is>
           <t>Quentin Johnson</t>
         </is>
       </c>
-      <c r="D95" t="n">
+      <c r="D95" s="3" t="n">
         <v>773</v>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
         <is>
           <t>[Asset Freeze]</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
         <is>
           <t>Inconsistent information from sanctions lists</t>
         </is>
       </c>
+      <c r="I95" s="4" t="n">
+        <v>46266.80070601852</v>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" t="n">
+      <c r="A96" s="3" t="n">
         <v>1814</v>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B96" s="3" t="inlineStr">
         <is>
           <t>Isabel Martin</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" s="3" t="inlineStr">
         <is>
           <t>I. Martin</t>
         </is>
       </c>
-      <c r="D96" t="n">
+      <c r="D96" s="3" t="n">
         <v>650</v>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
         <is>
           <t>Name read from id doesn’t exactly match customer name</t>
         </is>
       </c>
+      <c r="I96" s="4" t="n">
+        <v>46267.19403935185</v>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" t="n">
+      <c r="A97" s="3" t="n">
         <v>1828</v>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="3" t="inlineStr">
         <is>
           <t>Benjamin Brown</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C97" s="3" t="inlineStr">
         <is>
           <t>Benjamin Brown</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
         <is>
           <t>Missing credit score</t>
         </is>
       </c>
+      <c r="I97" s="4" t="n">
+        <v>46267.15402777777</v>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" t="n">
+      <c r="A98" s="3" t="n">
         <v>1889</v>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="3" t="inlineStr">
         <is>
           <t>Nathan Wright</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C98" s="3" t="inlineStr">
         <is>
           <t>Nathan Wright</t>
         </is>
       </c>
-      <c r="D98" t="n">
+      <c r="D98" s="3" t="n">
         <v>613</v>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
         <is>
           <t>[Arms Embargo]</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
         <is>
           <t>Inconsistent information from sanctions lists</t>
         </is>
       </c>
+      <c r="I98" s="4" t="n">
+        <v>46267.13877314814</v>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" t="n">
+      <c r="A99" s="3" t="n">
         <v>1919</v>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="3" t="inlineStr">
         <is>
           <t>Amelia Wright</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C99" s="3" t="inlineStr">
         <is>
           <t>A. Wright</t>
         </is>
       </c>
-      <c r="D99" t="n">
+      <c r="D99" s="3" t="n">
         <v>756</v>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
         <is>
           <t>Name read from id doesn’t exactly match customer name</t>
         </is>
       </c>
+      <c r="I99" s="4" t="n">
+        <v>46266.76832175926</v>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" t="n">
+      <c r="A100" s="3" t="n">
         <v>1961</v>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B100" s="3" t="inlineStr">
         <is>
           <t>Jack Wilson</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C100" s="3" t="inlineStr">
         <is>
           <t>Jack Wilson</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
         <is>
           <t>Missing credit score</t>
         </is>
       </c>
+      <c r="I100" s="4" t="n">
+        <v>46266.91652777778</v>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" t="n">
+      <c r="A101" s="3" t="n">
         <v>1993</v>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="3" t="inlineStr">
         <is>
           <t>Amelia Martin</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C101" s="3" t="inlineStr">
         <is>
           <t>Amelia Martin</t>
         </is>
       </c>
-      <c r="D101" t="n">
+      <c r="D101" s="3" t="n">
         <v>744</v>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
         <is>
           <t>[Travel Ban]</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>FLAGGED</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
         <is>
           <t>Inconsistent information from sanctions lists</t>
         </is>
+      </c>
+      <c r="I101" s="4" t="n">
+        <v>46266.79027777778</v>
       </c>
     </row>
   </sheetData>
